--- a/output/pdf_financials_xlsx/APMI.xlsx
+++ b/output/pdf_financials_xlsx/APMI.xlsx
@@ -3368,25 +3368,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.026427</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.096411</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.100356</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.100356</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.100356</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.100356</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.100356</v>
       </c>
     </row>
     <row r="93">
@@ -5550,7 +5550,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -6076,7 +6080,11 @@
           <t>Reserves 7,8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -6700,7 +6708,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6872,7 +6884,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/APMI.xlsx
+++ b/output/pdf_financials_xlsx/APMI.xlsx
@@ -765,22 +765,22 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000321</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002521</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004283</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.017864</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.014131</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001617</v>
       </c>
     </row>
     <row r="13">
@@ -1274,22 +1274,22 @@
         <v>-0.118079</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.137128</v>
+        <v>-0.137449</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.139419</v>
+        <v>-0.14194</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.414741</v>
+        <v>-0.419024</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.165984</v>
+        <v>-0.183848</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.270319</v>
+        <v>-0.28445</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.199112</v>
+        <v>-0.200729</v>
       </c>
     </row>
     <row r="28">
@@ -1336,22 +1336,22 @@
         <v>-0.118079</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.137128</v>
+        <v>-0.137449</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.139419</v>
+        <v>-0.14194</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.414741</v>
+        <v>-0.419024</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.165984</v>
+        <v>-0.183848</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.270319</v>
+        <v>-0.28445</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.199112</v>
+        <v>-0.200729</v>
       </c>
     </row>
     <row r="30">
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000371</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.591483</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.517895</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.346532</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.7517</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.559912</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.160792</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.062202</v>
       </c>
     </row>
     <row r="35">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000371</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.591483</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.517895</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.346532</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.7517</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.559912</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.160792</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.062202</v>
       </c>
     </row>
     <row r="37">
@@ -1927,28 +1927,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.000371</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.591483</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.517895</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.296532</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.756307</v>
+        <v>0.004607</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.570374</v>
+        <v>0.010462</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.17267</v>
+        <v>0.011878</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.065829</v>
+        <v>0.003627</v>
       </c>
     </row>
     <row r="49">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/APMI.xlsx
+++ b/output/pdf_financials_xlsx/APMI.xlsx
@@ -2543,25 +2543,25 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -3582,10 +3582,8 @@
       <c r="H99" s="3" t="n">
         <v>-0.270319</v>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-0.199112</v>
       </c>
     </row>
     <row r="100">
@@ -3615,10 +3613,8 @@
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3646,12 +3642,10 @@
         <v>0.006675</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.006975</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0.015519</v>
       </c>
     </row>
     <row r="102">
@@ -3681,10 +3675,8 @@
       <c r="H102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3714,10 +3706,8 @@
       <c r="H103" s="3" t="n">
         <v>-0.001414</v>
       </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" s="3" t="n">
+        <v>0.008251</v>
       </c>
     </row>
     <row r="104">
@@ -3747,10 +3737,8 @@
       <c r="H104" s="3" t="n">
         <v>-0.000468</v>
       </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="3" t="n">
+        <v>-0.000851</v>
       </c>
     </row>
     <row r="105">
@@ -3780,10 +3768,8 @@
       <c r="H105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3811,12 +3797,10 @@
         <v>0.012016</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.001882</v>
-      </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008857</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0.022919</v>
       </c>
     </row>
     <row r="107">
@@ -3846,10 +3830,8 @@
       <c r="H107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3879,10 +3861,8 @@
       <c r="H108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3912,10 +3892,8 @@
       <c r="H109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3945,10 +3923,8 @@
       <c r="H110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3978,10 +3954,8 @@
       <c r="H111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4011,10 +3985,8 @@
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4044,10 +4016,8 @@
       <c r="H113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -4077,10 +4047,8 @@
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -4110,10 +4078,8 @@
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -4143,10 +4109,8 @@
       <c r="H116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -4176,10 +4140,8 @@
       <c r="H117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -4209,10 +4171,8 @@
       <c r="H118" s="3" t="n">
         <v>-0.004755</v>
       </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I118" s="3" t="n">
+        <v>-0.112921</v>
       </c>
     </row>
     <row r="119">
@@ -4246,10 +4206,8 @@
       <c r="H119" s="3" t="n">
         <v>-0.119944</v>
       </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="3" t="n">
+        <v>-0.004995</v>
       </c>
     </row>
     <row r="120">
@@ -4279,10 +4237,8 @@
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -4312,10 +4268,8 @@
       <c r="H121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -4345,10 +4299,8 @@
       <c r="H122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -4378,10 +4330,8 @@
       <c r="H123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -4411,10 +4361,8 @@
       <c r="H124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -4444,10 +4392,8 @@
       <c r="H125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -4477,10 +4423,8 @@
       <c r="H126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -4557,10 +4501,8 @@
       <c r="H128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4594,10 +4536,8 @@
       <c r="H129" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="130">
@@ -4627,10 +4567,8 @@
       <c r="H130" s="3" t="n">
         <v>0.559912</v>
       </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="3" t="n">
+        <v>0.160792</v>
       </c>
     </row>
     <row r="131">
@@ -4660,10 +4598,8 @@
       <c r="H131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -4693,10 +4629,8 @@
       <c r="H132" s="3" t="n">
         <v>-0.39912</v>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="3" t="n">
+        <v>-0.09859</v>
       </c>
     </row>
     <row r="133">
@@ -4726,10 +4660,8 @@
       <c r="H133" s="3" t="n">
         <v>0.160792</v>
       </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="3" t="n">
+        <v>0.062202</v>
       </c>
     </row>
     <row r="134">
@@ -4759,10 +4691,8 @@
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -4792,10 +4722,8 @@
       <c r="H135" s="3" t="n">
         <v>-0.279176</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>-0.143595</v>
       </c>
     </row>
   </sheetData>
@@ -4809,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7024,10 +6952,8 @@
       <c r="K40" s="5" t="n">
         <v>-0.270319</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L40" s="5" t="n">
+        <v>-0.199112</v>
       </c>
     </row>
     <row r="41">
@@ -7038,12 +6964,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -7072,16 +6998,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>0.006675</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>-0.006975</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0.001766</v>
       </c>
     </row>
     <row r="42">
@@ -7097,39 +7025,49 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>(Increase) decrease in GST receivable</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.003954</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0.01131</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>-0.006444</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>0.044916</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>-0.04128</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>0.008862999999999999</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.000468</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.006975</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0.015519</v>
       </c>
     </row>
     <row r="43">
@@ -7145,7 +7083,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>(Increase) decrease in prepaid expenses</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7173,19 +7111,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>-0.054046</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>-0.003522</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K43" s="5" t="n">
         <v>-0.001414</v>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L43" s="5" t="n">
+        <v>0.008251</v>
       </c>
     </row>
     <row r="44">
@@ -7201,12 +7141,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>Decrease in accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -7219,25 +7159,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.073588</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>-0.094503</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>-0.477697</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.153968</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.279176</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000468</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.000851</v>
       </c>
     </row>
     <row r="45">
@@ -7248,19 +7194,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Acquisition of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Increase in due to related parties</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -7286,16 +7228,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>-0.001542</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.030832</v>
       </c>
     </row>
     <row r="46">
@@ -7306,15 +7250,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs – deposit</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -7325,33 +7273,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G46" s="5" t="n">
+        <v>-0.073588</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-0.094503</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>-0.477697</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-0.153968</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.115189</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.279176</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-0.143595</v>
       </c>
     </row>
     <row r="47">
@@ -7367,7 +7305,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs</t>
+          <t>Acquisition of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7390,22 +7328,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H47" s="5" t="n">
-        <v>-0.00945</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>-0.07052</v>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.03662</v>
+        <v>-0.0012</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.003213</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001542</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.005</v>
       </c>
     </row>
     <row r="48">
@@ -7421,14 +7361,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs - advance</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -7444,22 +7380,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>-0.03445</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>-0.12302</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>-0.03782</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.119944</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.115189</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>0.107926</v>
       </c>
     </row>
     <row r="49">
@@ -7475,12 +7415,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Exploration and evaluation costs</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -7498,26 +7438,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>-0.00945</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.07052</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.191788</v>
+        <v>-0.03662</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.39912</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003213</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.107921</v>
       </c>
     </row>
     <row r="50">
@@ -7533,12 +7467,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Cash used in investing activities</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7556,26 +7490,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H50" s="5" t="n">
+        <v>-0.03445</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.12302</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>0.7517</v>
+        <v>-0.03782</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.559912</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.119944</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.004995</v>
       </c>
     </row>
     <row r="51">
@@ -7586,19 +7514,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from loan payable</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -7624,16 +7548,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J51" s="5" t="n">
-        <v>0.559912</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>0.160792</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="52">
@@ -7644,12 +7570,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of exploration and evaluation asset $</t>
+          <t>Proceeds from loan payable to related party</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -7673,19 +7599,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="53">
@@ -7696,17 +7626,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Other receivables</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7714,36 +7644,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" s="5" t="n">
+        <v>0.697881</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>0.9575900000000001</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.03237</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>0.006675</v>
+        <v>0.005885</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L53" s="5" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="54">
@@ -7754,48 +7680,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Acquisition of exploration and evaluation asset</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.000371</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>0.591112</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.073588</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.828637</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.065</v>
+        <v>-0.594832</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.0012</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.191788</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.39912</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.09859</v>
       </c>
     </row>
     <row r="55">
@@ -7806,15 +7726,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sale of mineral tenure</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7825,33 +7749,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G55" s="5" t="n">
+        <v>0.591483</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>0.517895</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.346532</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.559912</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0.160792</v>
       </c>
     </row>
     <row r="56">
@@ -7867,10 +7781,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Recovery of share issuance cost</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -7881,33 +7799,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G56" s="5" t="n">
+        <v>0.517895</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>1.346532</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.005885</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7517</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.559912</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.160792</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>0.062202</v>
       </c>
     </row>
     <row r="57">
@@ -7918,52 +7826,46 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Shares issued for acquisition of exploration and evaluation asset $</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.697881</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n">
-        <v>0.9575900000000001</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>0.005885</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0315</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>0.0045</v>
       </c>
     </row>
     <row r="58">
@@ -7974,41 +7876,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0.000371</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.591112</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.073588</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0.828637</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>-0.594832</v>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="5" t="n">
-        <v>-0.191788</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006675</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.006975</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -8024,45 +7934,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.003954</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.01131</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.591483</v>
+        <v>-0.006444</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.517895</v>
+        <v>0.044916</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>1.346532</v>
+        <v>-0.04128</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>0.7517</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008862999999999999</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>-0.000468</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -8078,17 +7982,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8101,22 +8005,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.517895</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>1.346532</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.7517</v>
+        <v>-0.054046</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0.559912</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003522</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>-0.001414</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -8132,12 +8038,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Accounts payable in exploration and evaluation asset – prior year $</t>
+          <t>Exploration and evaluation costs – deposit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -8161,18 +8067,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n">
-        <v>-0.00315</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K61" s="5" t="n">
+        <v>-0.115189</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -8188,17 +8094,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -8221,18 +8127,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
-        <v>0.03237</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-0.191788</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>-0.39912</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -8253,10 +8157,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Exploration and evaluation deposit</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -8277,18 +8185,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.049439</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0.7517</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>0.559912</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -8304,15 +8210,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Net proceeds from share issuance</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8328,23 +8238,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="5" t="n">
-        <v>0.9575900000000001</v>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J64" s="5" t="n">
+        <v>0.559912</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0.160792</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -8360,15 +8268,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Accounts receivable – share subscription proceeds $</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Other receivables</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -8384,18 +8296,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.03237</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>0.006675</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8416,12 +8326,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Accounts payable in exploration and evaluation asset - prior year</t>
+          <t>Acquisition of exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -8440,18 +8350,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-0.00315</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.065</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-0.0012</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -8472,19 +8378,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of exploration and evaluation assets $</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Sale of mineral tenure</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -8500,11 +8402,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="5" t="n">
-        <v>0.02</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.0315</v>
+        <v>0.0125</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -8530,19 +8434,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Recovery of share issuance cost</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8553,18 +8453,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>0.069984</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="5" t="n">
+        <v>0.005885</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -8590,20 +8490,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>July 31, February</t>
+          <t>Accounts payable in exploration and evaluation asset – prior year $</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>2e-05</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8615,10 +8519,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="5" t="n">
+        <v>-0.00315</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -8644,20 +8546,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2019 to July</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8669,10 +8579,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="5" t="n">
+        <v>0.03237</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -8698,24 +8606,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cash (used in) provided by operating activities</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>0.000371</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.106769</v>
+          <t>Exploration and evaluation deposit</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8727,10 +8635,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="5" t="n">
+        <v>-0.049439</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -8761,27 +8667,31 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Proceeds from share issuance</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Net proceeds from share issuance</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>0.7524999999999999</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H72" s="5" t="n">
+        <v>0.9575900000000001</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -8812,36 +8722,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Accounts receivable – share subscription proceeds $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F73" s="5" t="n">
-        <v>-0.054619</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -8872,26 +8778,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Accounts payable in exploration and evaluation asset - prior year</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.000371</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -8903,10 +8807,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="5" t="n">
+        <v>-0.00315</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -8932,39 +8834,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
+          <t>Shares issued for acquisition of exploration and evaluation assets $</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0.000371</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.591483</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0.0315</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -8990,15 +8892,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Balance, incorporation on February 20, 2018 - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -9009,10 +8915,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" s="5" t="n">
+        <v>0.069984</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -9048,24 +8952,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Period from</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Issuance of seed shares 1 - -</t>
+          <t>July 31, February</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>2e-05</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9106,24 +9006,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Period from</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>2019 to July</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>-0.003583</v>
+        <v>0.002018</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.003583</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9164,20 +9060,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2018 1 - -</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Cash (used in) provided by operating activities</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
-        <v>-0.003583</v>
+        <v>0.000371</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.003583</v>
+        <v>-0.106769</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9218,22 +9118,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Initial public offering 5,000,000 500,000 -</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from share issuance</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.7524999999999999</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9274,22 +9178,26 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Private placements 5,050,000 252,500 -</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.2525</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.054619</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9330,22 +9238,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Share issue costs - (54,619) -</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>-0.054619</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.000371</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9386,24 +9298,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Share issue costs – agent options - (26,427) 26,427</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of period $</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.000371</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.591483</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9449,15 +9361,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2019 10,050,001 $ 671,454 $ 26,427 $</t>
+          <t>Balance, incorporation on February 20, 2018 - $ - $ - $</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.576219</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.121662</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -9493,24 +9409,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Consulting 9 $</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Issuance of seed shares 1 - -</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -9526,54 +9438,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="5" t="n">
-        <v>0.007875</v>
-      </c>
-      <c r="I85" s="5" t="n">
-        <v>0.134</v>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K85" s="5" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>0.042</v>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Office 9</t>
+          <t>Net loss - - -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-0.003583</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-0.003583</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -9585,49 +9501,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n">
-        <v>0.067151</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>0.08401</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0.125261</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>0.059411</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, July 31, 2018 1 - -</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>-0.003583</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-0.003583</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -9639,44 +9555,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>0.183662</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>0.08011600000000001</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>0.098146</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>0.079833</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Shareholder communication</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Initial public offering 5,000,000 500,000 -</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9703,38 +9621,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K88" s="5" t="n">
-        <v>0.013424</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>0.012206</v>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Transfer agent fees and filing fees</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Private placements 5,050,000 252,500 -</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>0.2525</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9761,84 +9677,90 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K89" s="5" t="n">
-        <v>0.012619</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>0.007279</v>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issue costs - (54,619) -</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>-0.054619</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G90" s="5" t="n">
-        <v>0.137449</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>0.14194</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>0.419024</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>0.183848</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>0.28445</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>0.200729</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Share issue costs – agent options - (26,427) 26,427</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -9849,73 +9771,89 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" s="5" t="n">
-        <v>0.000321</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0.002521</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>0.004283</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>0.017864</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>0.014131</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>0.001617</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.137128</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-0.139419</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.414741</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.165984</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.270319</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.199112</v>
+          <t>Balance, July 31, 2019 10,050,001 $ 671,454 $ 26,427 $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>0.576219</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.121662</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -9931,12 +9869,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Consulting 9 $</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9944,26 +9882,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>-3.9e-07</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.007875</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.134</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.035</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="94">
@@ -9979,10 +9923,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Office 9</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -9993,23 +9941,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" s="5" t="n">
-        <v>5.100001</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>5.11575</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>20.830001</v>
+        <v>0.067151</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>20.984522</v>
+        <v>0.08401</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>21.30278</v>
+        <v>0.125261</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>21.836576</v>
+        <v>0.059411</v>
       </c>
     </row>
     <row r="95">
@@ -10020,15 +9972,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves         Deficit            Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 21,130,001 $ 1,753,484 $ 100,356 $</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Professional fees 9</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -10049,21 +10005,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="5" t="n">
+        <v>0.183662</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.08011600000000001</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>0.874906</v>
+        <v>0.098146</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.978934</v>
+        <v>0.079833</v>
       </c>
     </row>
     <row r="96">
@@ -10074,15 +10026,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Issuance of shares for option payment</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pine Channel property 700,000 46,500 -</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -10114,12 +10070,10 @@
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013424</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>0.012206</v>
       </c>
     </row>
     <row r="97">
@@ -10130,17 +10084,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Issuance of shares for option payment</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - -</t>
+          <t>Transfer agent fees and filing fees</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10174,10 +10128,10 @@
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-0.270319</v>
+        <v>0.012619</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>-0.270319</v>
+        <v>0.007279</v>
       </c>
     </row>
     <row r="98">
@@ -10188,15 +10142,19 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Issuance of shares for option payment</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 21,830,001 1,799,984 100,356</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -10207,31 +10165,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G98" s="5" t="n">
+        <v>0.137449</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>0.14194</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>0.419024</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>0.183848</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0.651087</v>
+        <v>0.28445</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>-1.249253</v>
+        <v>0.200729</v>
       </c>
     </row>
     <row r="99">
@@ -10242,15 +10192,19 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Issuance of shares for option payment</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pine Channel property 100,000 4,500 -</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -10261,33 +10215,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G99" s="5" t="n">
+        <v>0.000321</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.002521</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0.004283</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.017864</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014131</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>0.001617</v>
       </c>
     </row>
     <row r="100">
@@ -10298,15 +10242,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Issuance of shares for option payment</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2025 21,930 ,001 1,804,484 100,356</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -10317,31 +10265,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>-0.137128</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-0.139419</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.414741</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>-0.165984</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>0.456475</v>
+        <v>-0.270319</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-1.448365</v>
+        <v>-0.199112</v>
       </c>
     </row>
     <row r="101">
@@ -10350,48 +10290,46 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Note July 31, 2024 July</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="5" t="n">
+        <v>-3.9e-07</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0.002023</v>
+        <v>-1e-08</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="102">
@@ -10407,41 +10345,37 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F102" s="5" t="n">
-        <v>0.016664</v>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.001779</v>
+        <v>5.100001</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.025517</v>
+        <v>5.11575</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.000992</v>
+        <v>20.830001</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.004516</v>
+        <v>20.984522</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>0.007635</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.30278</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>21.836576</v>
       </c>
     </row>
     <row r="103">
@@ -10452,12 +10386,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves         Deficit            Total</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shareholder information</t>
+          <t>Balance, July 31, 2023 21,130,001 $ 1,753,484 $ 100,356 $</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -10466,28 +10400,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" s="5" t="n">
-        <v>0.002662</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0.000782</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>0.002805</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>0.024847</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>0.010519</v>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>0.013424</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.874906</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>-0.978934</v>
       </c>
     </row>
     <row r="104">
@@ -10498,19 +10440,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Issuance of shares for option payment</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Pine Channel property 700,000 46,500 -</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -10521,20 +10459,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G104" s="5" t="n">
-        <v>0.013109</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>0.010412</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>0.005233</v>
-      </c>
-      <c r="J104" s="5" t="n">
-        <v>0.004687</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>0.004984</v>
+        <v>0.0465</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -10550,15 +10496,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves         Deficit           Total</t>
+          <t>Issuance of shares for option payment</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 20,830,001 $ 1,732,484 $ 100,356 $</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -10584,16 +10534,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n">
-        <v>1.01989</v>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>-0.81295</v>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.270319</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>-0.270319</v>
       </c>
     </row>
     <row r="106">
@@ -10604,12 +10554,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>Issuance of shares for option payment</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Channel property 300,000 21,000 -</t>
+          <t>Balance, July 31, 2024 21,830,001 1,799,984 100,356</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -10633,21 +10583,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0.651087</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>-1.249253</v>
       </c>
     </row>
     <row r="107">
@@ -10658,19 +10608,15 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>Issuance of shares for option payment</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Pine Channel property 100,000 4,500 -</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -10681,20 +10627,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" s="5" t="n">
-        <v>-0.139419</v>
-      </c>
-      <c r="H107" s="5" t="n">
-        <v>-0.139419</v>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>-0.414741</v>
-      </c>
-      <c r="J107" s="5" t="n">
-        <v>-0.165984</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>-0.165984</v>
+        <v>0.0045</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -10710,12 +10664,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>Issuance of shares for option payment</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2023 21,130,001 $ 1,753,484 $ 100,356 $</t>
+          <t>Balance, July 31, 2025 21,930 ,001 1,804,484 100,356</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -10739,19 +10693,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="5" t="n">
-        <v>0.874906</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0.874906</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K108" s="5" t="n">
-        <v>-0.978934</v>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.456475</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>-1.448365</v>
       </c>
     </row>
     <row r="109">
@@ -10760,14 +10716,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Issuance of shares for acquisition of Pine</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Channel property 700,000 46,500 -</t>
+          <t>Note July 31, 2024 July</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -10797,12 +10749,10 @@
         </is>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -10818,45 +10768,41 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2024 21,830,001 $ 1,799,984 $ 100,356 $</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>0.016664</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.001779</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0.025517</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.000992</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0.651087</v>
+        <v>0.004516</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>-1.249253</v>
+        <v>0.007635</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -10870,10 +10816,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Note July 31, 2023 July</t>
+          <t>Shareholder information</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -10882,31 +10832,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" s="5" t="n">
+        <v>0.002662</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.000782</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.002805</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.024847</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010519</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>0.013424</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -10927,7 +10869,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -10940,31 +10882,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>0.002077</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.013109</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0.010412</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.003139</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005233</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0.004687</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0.004984</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -10980,12 +10916,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Number      Amount      Reserves         Deficit           Total</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 20,530,001 $ 1,695,099 $ 100,356 $</t>
+          <t>Balance, July 31, 2022 20,830,001 $ 1,732,484 $ 100,356 $</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -11009,16 +10945,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="5" t="n">
-        <v>1.397246</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J113" s="5" t="n">
-        <v>-0.398209</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.01989</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>-0.81295</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -11039,7 +10975,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Channel property 300,000 31,500 -</t>
+          <t>Channel property 300,000 21,000 -</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -11058,16 +10994,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H114" s="5" t="n">
-        <v>0.0315</v>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.021</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -11093,10 +11029,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Recovery of share issuance costs - 5,885 -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -11107,26 +11047,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="5" t="n">
+        <v>-0.139419</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.005885</v>
+        <v>-0.139419</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0.005885</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.414741</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>-0.165984</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>-0.165984</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -11147,7 +11081,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 20,830,001 1,732,484 100,356</t>
+          <t>Balance, July 31, 2023 21,130,001 $ 1,753,484 $ 100,356 $</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -11172,15 +11106,13 @@
         </is>
       </c>
       <c r="I116" s="5" t="n">
-        <v>1.01989</v>
+        <v>0.874906</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>-0.81295</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.874906</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>-0.978934</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -11194,10 +11126,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Issuance of shares for acquisition of Pine</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Note July 31, 2022 July</t>
+          <t>Channel property 700,000 46,500 -</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -11216,16 +11152,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>0.0465</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -11246,43 +11184,45 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0.000143</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.000492</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.000367</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>0.000528</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>0.067151</v>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, July 31, 2024 21,830,001 $ 1,799,984 $ 100,356 $</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0.651087</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>-1.249253</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -11296,40 +11236,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
-        </is>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>0.00344</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>0.046146</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>0.015547</v>
-      </c>
-      <c r="H119" s="5" t="n">
-        <v>0.094803</v>
+          <t>Note July 31, 2023 July</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I119" s="5" t="n">
-        <v>0.183662</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -11350,33 +11288,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2020 10,050,001 $ 671,454 $ 96,411 $</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.5090750000000001</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>0.5090750000000001</v>
+      <c r="F120" s="5" t="n">
+        <v>0.002077</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I120" s="5" t="n">
-        <v>-0.25879</v>
+        <v>0.003139</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -11407,7 +11351,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Issuance of units for cash 10,270,000 1,027,000 -</t>
+          <t>Balance, July 31, 2021 20,530,001 $ 1,695,099 $ 100,356 $</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -11421,21 +11365,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="H121" s="5" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>1.397246</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>-0.398209</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -11456,12 +11400,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Exercise of stock options 10,000 1,529 (529)</t>
+          <t>Channel property 300,000 31,500 -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -11475,16 +11419,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>0.001</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0315</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.0315</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -11515,7 +11459,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Channel property 200,000 20,000</t>
+          <t>Recovery of share issuance costs - 5,885 -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -11529,16 +11473,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>0.02</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005885</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.005885</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -11569,7 +11513,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Issuance of finder warrants - (4,474) 4,474</t>
+          <t>Balance, July 31, 2022 20,830,001 1,732,484 100,356</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -11593,15 +11537,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="5" t="n">
+        <v>1.01989</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>-0.81295</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -11620,14 +11560,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Issuance of shares for acquisition of Pine</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Share issuance costs - (20,410) -</t>
+          <t>Note July 31, 2022 July</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -11641,16 +11577,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G125" s="5" t="n">
-        <v>-0.02041</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>-0.02041</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -11676,35 +11612,33 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 20,530,001 1,695,099 100,356</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0.000143</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0.000492</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.000367</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>1.397246</v>
+        <v>0.000528</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>-0.398209</v>
+        <v>0.067151</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -11730,35 +11664,33 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Issuance of shares for acquisition of Pine</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2022 20,830,001 $ 1,732,484 $ 100,356 $</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0.046146</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.015547</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>1.01989</v>
+        <v>0.094803</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>-0.81295</v>
+        <v>0.183662</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -11782,10 +11714,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Note July 31, 2021 July</t>
+          <t>Balance, July 31, 2020 10,050,001 $ 671,454 $ 96,411 $</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -11800,15 +11736,13 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.00202</v>
+        <v>0.5090750000000001</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5090750000000001</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>-0.25879</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -11834,19 +11768,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Consulting 8 $</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Issuance of units for cash 10,270,000 1,027,000 -</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11858,10 +11788,10 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.035881</v>
+        <v>1.027</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.007875</v>
+        <v>1.027</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -11892,12 +11822,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Share-based payments 6</t>
+          <t>Exercise of stock options 10,000 1,529 (529)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -11912,12 +11842,10 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.069984</v>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -11948,12 +11876,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2019 10,050,001 $ 671,454 $ 26,427 $</t>
+          <t>Channel property 200,000 20,000</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -11968,10 +11896,10 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.576219</v>
+        <v>0.02</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>-0.121662</v>
+        <v>0.02</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -12002,12 +11930,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Share-based payments - - 69,984</t>
+          <t>Issuance of finder warrants - (4,474) 4,474</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -12021,8 +11949,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G132" s="5" t="n">
-        <v>0.069984</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -12058,19 +11988,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Number      Amount      Reserves        Deficit          Total</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (20,410) -</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -12082,10 +12008,10 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>-0.137128</v>
+        <v>-0.02041</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>-0.137128</v>
+        <v>-0.02041</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -12121,7 +12047,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Balance, July 31, 2021 20,530,001 $ 1,695,099 $ 100,356 $</t>
+          <t>Balance, July 31, 2021 20,530,001 1,695,099 100,356</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -12135,16 +12061,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G134" s="5" t="n">
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
         <v>1.397246</v>
       </c>
-      <c r="H134" s="5" t="n">
+      <c r="I134" s="5" t="n">
         <v>-0.398209</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -12170,41 +12096,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>Issuance of shares for acquisition of Pine</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Consulting $</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Balance, July 31, 2022 20,830,001 $ 1,732,484 $ 100,356 $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>0.024005</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="5" t="n">
+        <v>1.01989</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>-0.81295</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -12228,14 +12148,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
-        </is>
-      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Listing Cost</t>
+          <t>Note July 31, 2021 July</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -12244,18 +12160,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>0.026033</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -12291,29 +12205,29 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period $</t>
+          <t>Consulting 8 $</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="n">
-        <v>-0.003583</v>
-      </c>
-      <c r="F137" s="5" t="n">
-        <v>-0.118079</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.035881</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>0.007875</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -12349,48 +12263,500 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
+          <t>Share-based payments 6</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.069984</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2019 10,050,001 $ 671,454 $ 26,427 $</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.576219</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-0.121662</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Share-based payments - - 69,984</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>0.069984</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Number      Amount      Reserves        Deficit          Total</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>-0.137128</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>-0.137128</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Issuance of shares for acquisition of Pine</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Balance, July 31, 2021 20,530,001 $ 1,695,099 $ 100,356 $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>1.397246</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>-0.398209</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Consulting $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>0.024005</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Listing Cost</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>0.026033</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-0.003583</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-0.118079</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" s="5" t="n">
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n">
         <v>0.30137</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
